--- a/LubanConfig/MiniTemplate/Datas/#numdemand.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/#numdemand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>建造3个棉花农场</t>
-  </si>
-  <si>
-    <t xml:space="preserve">building </t>
   </si>
   <si>
     <t>建造4个小麦农场</t>
@@ -1228,10 +1225,10 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -1251,7 +1248,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:7">
@@ -1271,7 +1268,7 @@
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -1291,7 +1288,7 @@
         <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -1311,7 +1308,7 @@
         <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="2:7">
@@ -1331,7 +1328,7 @@
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -1351,7 +1348,7 @@
         <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="2:7">
@@ -1371,7 +1368,7 @@
         <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -1391,7 +1388,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -1408,10 +1405,10 @@
         <v>200000</v>
       </c>
       <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
         <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -1428,10 +1425,10 @@
         <v>400000</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="2:7">
@@ -1448,10 +1445,10 @@
         <v>600000</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -1468,10 +1465,10 @@
         <v>1000000</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
